--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Gold ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Gold ETF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB10CC7-FD8B-4D88-82F6-4D3F80336520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EBBD91-620A-43F8-AD4C-8DDE647F61AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Gold ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,7 +76,7 @@
     <t>^ - Physical Gold.</t>
   </si>
   <si>
-    <t>Aggregate value of investments made by other schemes of ICICI Prudential Mutual Fund are amounting to Rs. 159169.13  Lakh.</t>
+    <t>Aggregate value of investments made by other schemes of ICICI Prudential Mutual Fund are amounting to Rs. 184629.88  Lakh.</t>
   </si>
   <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
@@ -85,7 +85,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -97,7 +97,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - LBMA AM fixing Prices (Domestic Price of Silver) (Benchmark)</t>
+    <t>Benchmark name - Domestic price of gold as derived from the LBMA AM fixing prices</t>
   </si>
 </sst>
 </file>
@@ -257,6 +257,21 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -283,6 +298,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -297,23 +313,7 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -761,305 +761,305 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="41.5703125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="6.5703125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="19.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="10.85546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="38.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="27.140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="23" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="41.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="6.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="19.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="10.85546875" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="38.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="11.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="27.140625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="8">
-        <v>687594</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0.98326626566370001</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="C5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="12">
+        <v>744553.56</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.98663698038570002</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="12">
-        <v>8406</v>
-      </c>
-      <c r="F6" s="13">
-        <v>687594</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0.98326626566370001</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="E6" s="17">
+        <v>7816</v>
+      </c>
+      <c r="F6" s="18">
+        <v>744553.56</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0.98663698038570002</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="B7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="8">
-        <v>108.75</v>
-      </c>
-      <c r="G8" s="9">
-        <v>1.5551358270000001E-4</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="C8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="12">
+        <v>131.38999999999999</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1.741100168E-4</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="B9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="16">
-        <v>11593.080652600038</v>
-      </c>
-      <c r="G10" s="17">
-        <v>1.6578220753555889E-2</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="C10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="21">
+        <v>9952.8497192999348</v>
+      </c>
+      <c r="G10" s="22">
+        <v>1.3188909597428146E-2</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="16">
-        <v>699295.83065260004</v>
-      </c>
-      <c r="G11" s="17">
-        <v>0.99999999999995592</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="C11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="21">
+        <v>754637.7997193</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0.99999999999992817</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="22" spans="2:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="23" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="23" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="23" t="s">
         <v>25</v>
       </c>
     </row>
